--- a/projeto hotel/db/clientes.xlsx
+++ b/projeto hotel/db/clientes.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>087.280.297-39</t>
+          <t>02402402403</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1348,6 +1348,46 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ana banana</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>68366699932</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sam@winchester</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>7458+96332</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>banker</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> fez xixi na cama</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
